--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484845_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484845_PROCESSED_CHRONO.xlsx
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.4624</v>
+        <v>-0.2146</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1506</v>
+        <v>0.0442</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.3117</v>
+        <v>-0.2588</v>
       </c>
       <c r="G3" t="n">
         <v>-0.5709</v>
@@ -688,13 +688,13 @@
         <v>0.3774</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5896</v>
+        <v>-0.3418</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2352</v>
+        <v>-0.0403</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3545</v>
+        <v>-0.3016</v>
       </c>
       <c r="V3" t="n">
         <v>0.3208</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>I. ALAMINOS HERNANDEZ</t>
+          <t>C. GILABERT FERRI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.5784</v>
+        <v>-0.6803</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2945</v>
+        <v>-1.0837</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.8729</v>
+        <v>0.4034</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.5741000000000001</v>
+        <v>-2.0289</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1628</v>
+        <v>-3.3065</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4113</v>
+        <v>1.2776</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4069</v>
+        <v>-0.7865</v>
       </c>
       <c r="K4" t="n">
-        <v>1.0565</v>
+        <v>-0.7865</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.6496</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.981</v>
+        <v>-1.2424</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.2193</v>
+        <v>-2.5199</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2383</v>
+        <v>1.2776</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3774</v>
+        <v>1.3209</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3774</v>
+        <v>1.3209</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8635</v>
+        <v>0.3295</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8875999999999999</v>
+        <v>-0.2972</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0241</v>
+        <v>0.6267</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.2452</v>
+        <v>-0.3018</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2452</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C. GILABERT FERRI</t>
+          <t>I. ALAMINOS HERNANDEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.0121</v>
+        <v>-1.0042</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.7859</v>
+        <v>0.7099</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7738</v>
+        <v>-1.7142</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.0289</v>
+        <v>-0.5741000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>-3.3065</v>
+        <v>-0.1628</v>
       </c>
       <c r="I5" t="n">
-        <v>1.2776</v>
+        <v>-0.4113</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.7865</v>
+        <v>0.4069</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.7865</v>
+        <v>1.0565</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-0.6496</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.2424</v>
+        <v>-0.981</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.5199</v>
+        <v>-1.2193</v>
       </c>
       <c r="O5" t="n">
-        <v>1.2776</v>
+        <v>0.2383</v>
       </c>
       <c r="P5" t="n">
-        <v>1.3209</v>
+        <v>0.3774</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3209</v>
+        <v>0.3774</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0023</v>
+        <v>0.4376</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9994</v>
+        <v>0.303</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9971</v>
+        <v>0.1346</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3018</v>
+        <v>-1.2452</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.3018</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.0527</v>
+        <v>-1.2837</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6576</v>
+        <v>0.2679</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.7103</v>
+        <v>-1.5516</v>
       </c>
       <c r="G6" t="n">
         <v>-1.5097</v>
@@ -922,13 +922,13 @@
         <v>0.5661</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2222</v>
+        <v>-0.4532</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3585</v>
+        <v>-0.0312</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5808</v>
+        <v>-0.422</v>
       </c>
       <c r="V6" t="n">
         <v>0.3018</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.293</v>
+        <v>-1.7504</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.3935</v>
+        <v>-2.6657</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1005</v>
+        <v>0.9153</v>
       </c>
       <c r="G7" t="n">
         <v>-0.2434</v>
@@ -1000,13 +1000,13 @@
         <v>0.9435</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5355</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0029</v>
+        <v>-0.2693</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5326</v>
+        <v>0.3475</v>
       </c>
       <c r="V7" t="n">
         <v>0.3018</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.1179</v>
+        <v>-2.2094</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2981</v>
+        <v>0.2594</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.4159</v>
+        <v>-2.4689</v>
       </c>
       <c r="G8" t="n">
         <v>0.1373</v>
@@ -1078,13 +1078,13 @@
         <v>1.5096</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.425</v>
+        <v>-0.5165999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2323</v>
+        <v>-0.2709</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1928</v>
+        <v>-0.2457</v>
       </c>
       <c r="V8" t="n">
         <v>-2.2076</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>B. TERREROS RIVAS</t>
+          <t>B. ZHENG</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.0992</v>
+        <v>-2.8861</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.1144</v>
+        <v>-2.6086</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0151</v>
+        <v>-0.2775</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.8123</v>
+        <v>-1.2573</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.7908</v>
+        <v>-2.0152</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0216</v>
+        <v>0.7579</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.5294</v>
+        <v>-0.5017</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.8798</v>
+        <v>0.1479</v>
       </c>
       <c r="L9" t="n">
         <v>-0.6496</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2829</v>
+        <v>-0.7556</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9109</v>
+        <v>-2.1631</v>
       </c>
       <c r="O9" t="n">
-        <v>0.628</v>
+        <v>1.4075</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.5096</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.887</v>
+        <v>-1.3209</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3774</v>
+        <v>1.3209</v>
       </c>
       <c r="S9" t="n">
-        <v>1.2227</v>
+        <v>-1.365</v>
       </c>
       <c r="T9" t="n">
-        <v>1.302</v>
+        <v>-0.786</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0793</v>
+        <v>-0.579</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.2639</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.2639</v>
       </c>
     </row>
     <row r="10">
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.4388</v>
+        <v>-3.1851</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.7775</v>
+        <v>-3.5238</v>
       </c>
       <c r="F10" t="n">
         <v>0.3387</v>
@@ -1234,10 +1234,10 @@
         <v>1.6983</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2352</v>
+        <v>0.0185</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8201000000000001</v>
+        <v>-0.5665</v>
       </c>
       <c r="U10" t="n">
         <v>0.585</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>B. ZHENG</t>
+          <t>B. TERREROS RIVAS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.7314</v>
+        <v>-4.1</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.0571</v>
+        <v>-4.0887</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.6743</v>
+        <v>-0.0113</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.2573</v>
+        <v>-2.8123</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.0152</v>
+        <v>-2.7908</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7579</v>
+        <v>-0.0216</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.5017</v>
+        <v>-2.5294</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1479</v>
+        <v>-1.8798</v>
       </c>
       <c r="L11" t="n">
         <v>-0.6496</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.7556</v>
+        <v>-0.2829</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.1631</v>
+        <v>-0.9109</v>
       </c>
       <c r="O11" t="n">
-        <v>1.4075</v>
+        <v>0.628</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-1.5096</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.3209</v>
+        <v>-1.887</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3209</v>
+        <v>0.3774</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.2103</v>
+        <v>0.2219</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.2345</v>
+        <v>0.3277</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.9758</v>
+        <v>-0.1058</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.2639</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.2639</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.9124</v>
+        <v>-4.1354</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.7242</v>
+        <v>-1.7885</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.1882</v>
+        <v>-2.3469</v>
       </c>
       <c r="G12" t="n">
         <v>-3.0248</v>
@@ -1390,13 +1390,13 @@
         <v>1.3209</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9441000000000001</v>
+        <v>-0.1671</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.2933</v>
+        <v>-0.3576</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3492</v>
+        <v>0.1905</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.5349</v>
+        <v>-7.196</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.4915</v>
+        <v>-6.1791</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.0434</v>
+        <v>-1.0169</v>
       </c>
       <c r="G13" t="n">
         <v>-5.4036</v>
@@ -1468,13 +1468,13 @@
         <v>1.5096</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.0558</v>
+        <v>-0.7169</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.2345</v>
+        <v>-0.9221</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1788</v>
+        <v>0.2052</v>
       </c>
       <c r="V13" t="n">
         <v>-0.3208</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-27.3315</v>
+        <v>-26.7435</v>
       </c>
       <c r="E14" t="n">
-        <v>-19.3428</v>
+        <v>-18.755</v>
       </c>
       <c r="F14" t="n">
-        <v>-7.9886</v>
+        <v>-7.9887</v>
       </c>
       <c r="G14" t="n">
         <v>-20.7962</v>
@@ -1516,7 +1516,7 @@
         <v>-19.1738</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.6226</v>
+        <v>-1.622599999999999</v>
       </c>
       <c r="J14" t="n">
         <v>-6.5585</v>
@@ -1537,7 +1537,7 @@
         <v>8.7704</v>
       </c>
       <c r="P14" t="n">
-        <v>-7.548000000000001</v>
+        <v>-7.548</v>
       </c>
       <c r="Q14" t="n">
         <v>-18.87</v>
@@ -1546,22 +1546,22 @@
         <v>11.322</v>
       </c>
       <c r="S14" t="n">
-        <v>-3.062800000000001</v>
+        <v>-2.4749</v>
       </c>
       <c r="T14" t="n">
-        <v>-3.4983</v>
+        <v>-2.9104</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4354</v>
+        <v>0.4354000000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>4.0753</v>
+        <v>4.075299999999999</v>
       </c>
       <c r="W14" t="n">
         <v>9.5838</v>
       </c>
       <c r="X14" t="n">
-        <v>-5.508500000000002</v>
+        <v>-5.5085</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>8.364599999999999</v>
+        <v>5.8243</v>
       </c>
       <c r="E15" t="n">
-        <v>5.8459</v>
+        <v>3.7024</v>
       </c>
       <c r="F15" t="n">
-        <v>2.5187</v>
+        <v>2.1219</v>
       </c>
       <c r="G15" t="n">
         <v>4.1256</v>
@@ -1624,13 +1624,13 @@
         <v>2.6418</v>
       </c>
       <c r="S15" t="n">
-        <v>4.0879</v>
+        <v>1.5475</v>
       </c>
       <c r="T15" t="n">
-        <v>3.2043</v>
+        <v>1.0607</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8836000000000001</v>
+        <v>0.4868</v>
       </c>
       <c r="V15" t="n">
         <v>-0.6036</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.1094</v>
+        <v>5.7205</v>
       </c>
       <c r="E16" t="n">
-        <v>2.5303</v>
+        <v>3.1149</v>
       </c>
       <c r="F16" t="n">
-        <v>2.5791</v>
+        <v>2.6056</v>
       </c>
       <c r="G16" t="n">
         <v>4.7288</v>
@@ -1702,13 +1702,13 @@
         <v>1.887</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2422</v>
+        <v>0.3689</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8695000000000001</v>
+        <v>-0.2849</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6273</v>
+        <v>0.6536999999999999</v>
       </c>
       <c r="V16" t="n">
         <v>-1.2642</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.5211</v>
+        <v>4.7702</v>
       </c>
       <c r="E17" t="n">
-        <v>2.8083</v>
+        <v>3.2955</v>
       </c>
       <c r="F17" t="n">
-        <v>1.7127</v>
+        <v>1.4747</v>
       </c>
       <c r="G17" t="n">
         <v>3.4611</v>
@@ -1780,13 +1780,13 @@
         <v>1.5096</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0905</v>
+        <v>0.1586</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5879</v>
+        <v>-0.1007</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4974</v>
+        <v>0.2593</v>
       </c>
       <c r="V17" t="n">
         <v>2.4714</v>
@@ -1813,10 +1813,10 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.3647</v>
+        <v>2.9493</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9828</v>
+        <v>1.5674</v>
       </c>
       <c r="F18" t="n">
         <v>1.3819</v>
@@ -1858,10 +1858,10 @@
         <v>1.5096</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6031</v>
+        <v>-0.0185</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6343</v>
+        <v>-0.0497</v>
       </c>
       <c r="U18" t="n">
         <v>0.0312</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.0477</v>
+        <v>2.6046</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8445</v>
+        <v>-0.5522</v>
       </c>
       <c r="F19" t="n">
-        <v>2.8922</v>
+        <v>3.1568</v>
       </c>
       <c r="G19" t="n">
         <v>1.7621</v>
@@ -1936,13 +1936,13 @@
         <v>2.6418</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5073</v>
+        <v>0.0495</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6438</v>
+        <v>-0.3515</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1365</v>
+        <v>0.401</v>
       </c>
       <c r="V19" t="n">
         <v>-1.8488</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. GARCIA RUIZ</t>
+          <t>A. VAICIUNAS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.0155</v>
+        <v>1.2385</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.3156</v>
+        <v>-0.211</v>
       </c>
       <c r="F20" t="n">
-        <v>2.3311</v>
+        <v>1.4496</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.8577</v>
+        <v>0.3855</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0517</v>
+        <v>0.08450000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.9094</v>
+        <v>0.301</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.0346</v>
+        <v>0.29</v>
       </c>
       <c r="K20" t="n">
-        <v>0.9141</v>
+        <v>0.8984</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.9487</v>
+        <v>-0.6084000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1769</v>
+        <v>0.0955</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8624000000000001</v>
+        <v>-0.8139</v>
       </c>
       <c r="O20" t="n">
-        <v>1.0393</v>
+        <v>0.9094</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9435</v>
+        <v>1.1322</v>
       </c>
       <c r="Q20" t="n">
         <v>-0.9435</v>
       </c>
       <c r="R20" t="n">
-        <v>1.887</v>
+        <v>2.0757</v>
       </c>
       <c r="S20" t="n">
-        <v>1.609</v>
+        <v>0.6643</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4173</v>
+        <v>-0.1611</v>
       </c>
       <c r="U20" t="n">
-        <v>1.1916</v>
+        <v>0.8254</v>
       </c>
       <c r="V20" t="n">
-        <v>0.3208</v>
+        <v>-0.9434</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2452</v>
+        <v>0.6036</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.9244</v>
+        <v>-1.547</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. VAICIUNAS</t>
+          <t>J. CALERO SEVILLANO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.0534</v>
+        <v>1.2189</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.211</v>
+        <v>-1.5857</v>
       </c>
       <c r="F21" t="n">
-        <v>1.2644</v>
+        <v>2.8046</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3855</v>
+        <v>1.3016</v>
       </c>
       <c r="H21" t="n">
-        <v>0.08450000000000001</v>
+        <v>1.7155</v>
       </c>
       <c r="I21" t="n">
-        <v>0.301</v>
+        <v>-0.4138</v>
       </c>
       <c r="J21" t="n">
-        <v>0.29</v>
+        <v>0.8321</v>
       </c>
       <c r="K21" t="n">
-        <v>0.8984</v>
+        <v>2.1553</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6084000000000001</v>
+        <v>-1.3232</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0955</v>
+        <v>0.4696</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.8139</v>
+        <v>-0.4398</v>
       </c>
       <c r="O21" t="n">
         <v>0.9094</v>
       </c>
       <c r="P21" t="n">
-        <v>1.1322</v>
+        <v>-0.1887</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9435</v>
+        <v>-1.887</v>
       </c>
       <c r="R21" t="n">
-        <v>2.0757</v>
+        <v>1.6983</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4791</v>
+        <v>0.106</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1611</v>
+        <v>-0.5306999999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6402</v>
+        <v>0.6367</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.9434</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.6036</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.547</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. CALERO SEVILLANO</t>
+          <t>V. BERENGUER DEL VALLE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.953</v>
+        <v>1.0515</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.878</v>
+        <v>1.3205</v>
       </c>
       <c r="F22" t="n">
-        <v>2.831</v>
+        <v>-0.269</v>
       </c>
       <c r="G22" t="n">
-        <v>1.3016</v>
+        <v>0.0197</v>
       </c>
       <c r="H22" t="n">
-        <v>1.7155</v>
+        <v>0.3271</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.4138</v>
+        <v>-0.3075</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8321</v>
+        <v>0.3468</v>
       </c>
       <c r="K22" t="n">
-        <v>2.1553</v>
+        <v>1.5636</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.3232</v>
+        <v>-1.2169</v>
       </c>
       <c r="M22" t="n">
-        <v>0.4696</v>
+        <v>-0.3271</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4398</v>
+        <v>-1.2365</v>
       </c>
       <c r="O22" t="n">
         <v>0.9094</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.1887</v>
+        <v>1.5096</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.887</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.6983</v>
+        <v>1.5096</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1599</v>
+        <v>-0.1569</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.823</v>
+        <v>0.0493</v>
       </c>
       <c r="U22" t="n">
-        <v>0.6631</v>
+        <v>-0.2063</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.3208</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.9244</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. PUJALTE MIRA</t>
+          <t>A. GARCIA RUIZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.5842000000000001</v>
+        <v>0.9812</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.8603</v>
+        <v>-0.9002</v>
       </c>
       <c r="F23" t="n">
-        <v>2.4445</v>
+        <v>1.8814</v>
       </c>
       <c r="G23" t="n">
-        <v>1.5812</v>
+        <v>-0.8577</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3623</v>
+        <v>0.0517</v>
       </c>
       <c r="I23" t="n">
-        <v>1.2189</v>
+        <v>-0.9094</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0238</v>
+        <v>-1.0346</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.0259</v>
+        <v>0.9141</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0496</v>
+        <v>-1.9487</v>
       </c>
       <c r="M23" t="n">
-        <v>1.5574</v>
+        <v>0.1769</v>
       </c>
       <c r="N23" t="n">
-        <v>0.3882</v>
+        <v>-0.8624000000000001</v>
       </c>
       <c r="O23" t="n">
-        <v>1.1692</v>
+        <v>1.0393</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.3774</v>
+        <v>0.9435</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.887</v>
+        <v>-0.9435</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5096</v>
+        <v>1.887</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6196</v>
+        <v>0.5746</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0029</v>
+        <v>-0.1673</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6225000000000001</v>
+        <v>0.7419</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>0.3208</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.2452</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-0.9244</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>V. BERENGUER DEL VALLE</t>
+          <t>J. PUJALTE MIRA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.3179</v>
+        <v>0.9726</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9308</v>
+        <v>-1.7629</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.6129</v>
+        <v>2.7355</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0197</v>
+        <v>1.5812</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3271</v>
+        <v>0.3623</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.3075</v>
+        <v>1.2189</v>
       </c>
       <c r="J24" t="n">
-        <v>0.3468</v>
+        <v>0.0238</v>
       </c>
       <c r="K24" t="n">
-        <v>1.5636</v>
+        <v>-0.0259</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.2169</v>
+        <v>0.0496</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.3271</v>
+        <v>1.5574</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.2365</v>
+        <v>0.3882</v>
       </c>
       <c r="O24" t="n">
-        <v>0.9094</v>
+        <v>1.1692</v>
       </c>
       <c r="P24" t="n">
-        <v>1.5096</v>
+        <v>-0.3774</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="R24" t="n">
         <v>1.5096</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8905999999999999</v>
+        <v>-0.2312</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3404</v>
+        <v>0.1003</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5502</v>
+        <v>-0.3315</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.3208</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>0.9244</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.2452</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>27.3315</v>
+        <v>27.3316</v>
       </c>
       <c r="E25" t="n">
         <v>7.9887</v>
       </c>
       <c r="F25" t="n">
-        <v>19.3427</v>
+        <v>19.343</v>
       </c>
       <c r="G25" t="n">
         <v>20.7964</v>
@@ -2395,7 +2395,7 @@
         <v>10.393</v>
       </c>
       <c r="P25" t="n">
-        <v>7.548000000000001</v>
+        <v>7.548</v>
       </c>
       <c r="Q25" t="n">
         <v>-11.322</v>
@@ -2404,19 +2404,19 @@
         <v>18.87</v>
       </c>
       <c r="S25" t="n">
-        <v>3.0628</v>
+        <v>3.062800000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.4354999999999998</v>
+        <v>-0.4355999999999998</v>
       </c>
       <c r="U25" t="n">
-        <v>3.498199999999999</v>
+        <v>3.4982</v>
       </c>
       <c r="V25" t="n">
         <v>-4.0754</v>
       </c>
       <c r="W25" t="n">
-        <v>5.508400000000001</v>
+        <v>5.5084</v>
       </c>
       <c r="X25" t="n">
         <v>-9.5838</v>
